--- a/output/roomself_excel/14951.xlsx
+++ b/output/roomself_excel/14951.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,10 +476,10 @@
         <v>2604</v>
       </c>
       <c r="E2" t="n">
-        <v>431</v>
+        <v>284</v>
       </c>
       <c r="F2" t="n">
-        <v>265</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3">
@@ -492,10 +492,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>192195</v>
+        <v>122360</v>
       </c>
       <c r="D3" t="n">
-        <v>5676</v>
+        <v>2808</v>
       </c>
       <c r="E3" t="n">
         <v>322</v>
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22728</v>
+        <v>77000</v>
       </c>
       <c r="D4" t="n">
-        <v>1220</v>
+        <v>2252</v>
       </c>
       <c r="E4" t="n">
-        <v>224</v>
+        <v>253</v>
       </c>
       <c r="F4" t="n">
-        <v>172</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>48750</v>
+        <v>101003</v>
       </c>
       <c r="D5" t="n">
-        <v>1900</v>
+        <v>2544</v>
       </c>
       <c r="E5" t="n">
-        <v>325</v>
+        <v>351</v>
       </c>
       <c r="F5" t="n">
-        <v>22</v>
+        <v>339</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>10604</v>
+        <v>48750</v>
       </c>
       <c r="D6" t="n">
-        <v>844</v>
+        <v>1900</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>325</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>77000</v>
+        <v>69835</v>
       </c>
       <c r="D7" t="n">
-        <v>2252</v>
+        <v>3220</v>
       </c>
       <c r="E7" t="n">
-        <v>253</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>101003</v>
+        <v>9393</v>
       </c>
       <c r="D8" t="n">
-        <v>2544</v>
+        <v>776</v>
       </c>
       <c r="E8" t="n">
-        <v>351</v>
+        <v>101</v>
       </c>
       <c r="F8" t="n">
-        <v>339</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,42 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>9393</v>
+        <v>10604</v>
       </c>
       <c r="D9" t="n">
-        <v>776</v>
+        <v>844</v>
       </c>
       <c r="E9" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>32</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>22728</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1220</v>
+      </c>
+      <c r="E10" t="n">
+        <v>224</v>
+      </c>
+      <c r="F10" t="n">
+        <v>172</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/14951.xlsx
+++ b/output/roomself_excel/14951.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,12 +495,20 @@
       <c r="D2" t="n">
         <v>2604</v>
       </c>
-      <c r="E2" t="n">
-        <v>284</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>71</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="G2" t="n">
+        <v>34</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,11 +525,27 @@
       <c r="D3" t="n">
         <v>2808</v>
       </c>
-      <c r="E3" t="n">
-        <v>322</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>52</v>
+        <v>300</v>
+      </c>
+      <c r="G3" t="n">
+        <v>33</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>380</v>
+      </c>
+      <c r="J3" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="4">
@@ -519,10 +563,26 @@
       <c r="D4" t="n">
         <v>2252</v>
       </c>
-      <c r="E4" t="n">
-        <v>253</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F4" t="n">
+        <v>310</v>
+      </c>
+      <c r="G4" t="n">
+        <v>35</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>243</v>
+      </c>
+      <c r="J4" t="n">
         <v>32</v>
       </c>
     </row>
@@ -541,11 +601,27 @@
       <c r="D5" t="n">
         <v>2544</v>
       </c>
-      <c r="E5" t="n">
-        <v>351</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>339</v>
+        <v>307</v>
+      </c>
+      <c r="G5" t="n">
+        <v>22</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>319</v>
+      </c>
+      <c r="J5" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="6">
@@ -563,12 +639,20 @@
       <c r="D6" t="n">
         <v>1900</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>325</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>22</v>
       </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +669,12 @@
       <c r="D7" t="n">
         <v>3220</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +691,20 @@
       <c r="D8" t="n">
         <v>776</v>
       </c>
-      <c r="E8" t="n">
-        <v>101</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>32</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="G8" t="n">
+        <v>14</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +721,20 @@
       <c r="D9" t="n">
         <v>844</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="G9" t="n">
+        <v>35</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,11 +751,27 @@
       <c r="D10" t="n">
         <v>1220</v>
       </c>
-      <c r="E10" t="n">
-        <v>224</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F10" t="n">
-        <v>172</v>
+        <v>121</v>
+      </c>
+      <c r="G10" t="n">
+        <v>34</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>153</v>
+      </c>
+      <c r="J10" t="n">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
